--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.29758640611621</v>
+        <v>4.598357790993884</v>
       </c>
       <c r="D2" t="n">
-        <v>78.87487212122196</v>
+        <v>12.81716671969857</v>
       </c>
       <c r="E2" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F2" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.97592974325363</v>
+        <v>4.058588583278715</v>
       </c>
       <c r="D3" t="n">
-        <v>56.83670070967991</v>
+        <v>9.235963865322987</v>
       </c>
       <c r="E3" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F3" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.05281411891355</v>
+        <v>8.621082294323452</v>
       </c>
       <c r="D4" t="n">
-        <v>46.42391429588703</v>
+        <v>7.543886073081643</v>
       </c>
       <c r="E4" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F4" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.31156300439547</v>
+        <v>8.175628988214266</v>
       </c>
       <c r="D5" t="n">
-        <v>47.52279810436114</v>
+        <v>7.722454691958686</v>
       </c>
       <c r="E5" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F5" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.47925097237125</v>
+        <v>8.202878283010328</v>
       </c>
       <c r="D6" t="n">
-        <v>53.45785960948756</v>
+        <v>8.686902186541728</v>
       </c>
       <c r="E6" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F6" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.162135785641307</v>
+        <v>0.8388470651667124</v>
       </c>
       <c r="D7" t="n">
-        <v>42.48183274868421</v>
+        <v>6.903297821661184</v>
       </c>
       <c r="E7" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F7" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.04076617259408</v>
+        <v>10.56912450304654</v>
       </c>
       <c r="D8" t="n">
-        <v>70.19249410248364</v>
+        <v>11.40628029165359</v>
       </c>
       <c r="E8" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F8" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.45707281366987</v>
+        <v>3.324274332221353</v>
       </c>
       <c r="D9" t="n">
-        <v>30.64381646488248</v>
+        <v>4.979620175543404</v>
       </c>
       <c r="E9" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F9" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.28476244688972</v>
+        <v>2.646273897619579</v>
       </c>
       <c r="D10" t="n">
-        <v>6.498742638781629</v>
+        <v>1.056045678802015</v>
       </c>
       <c r="E10" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F10" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.27751074753748</v>
+        <v>4.595095496474841</v>
       </c>
       <c r="D11" t="n">
-        <v>17.78050407323298</v>
+        <v>2.88933191190036</v>
       </c>
       <c r="E11" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F11" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.97090803167534</v>
+        <v>6.495272555147244</v>
       </c>
       <c r="D12" t="n">
-        <v>3.812045333348989</v>
+        <v>0.6194573666692108</v>
       </c>
       <c r="E12" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F12" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.74341292615576</v>
+        <v>3.370804600500311</v>
       </c>
       <c r="D13" t="n">
-        <v>21.51015905163472</v>
+        <v>3.495400845890642</v>
       </c>
       <c r="E13" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F13" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.49400449789876</v>
+        <v>2.030275730908549</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58925856189488</v>
+        <v>3.995754516307918</v>
       </c>
       <c r="E14" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F14" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.47226365682549</v>
+        <v>4.626742844234141</v>
       </c>
       <c r="D15" t="n">
-        <v>1.498893597040103</v>
+        <v>0.2435702095190167</v>
       </c>
       <c r="E15" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F15" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.29417403350282</v>
+        <v>2.647803280444209</v>
       </c>
       <c r="D16" t="n">
-        <v>17.93759487209838</v>
+        <v>2.914859166715987</v>
       </c>
       <c r="E16" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F16" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>20.13793826801738</v>
+        <v>3.272414968552825</v>
       </c>
       <c r="D17" t="n">
-        <v>18.73142245446749</v>
+        <v>3.043856148850967</v>
       </c>
       <c r="E17" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F17" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>36.35755649102129</v>
+        <v>5.90810292979096</v>
       </c>
       <c r="D18" t="n">
-        <v>34.86596213655174</v>
+        <v>5.665718847189659</v>
       </c>
       <c r="E18" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F18" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>32.81511727799115</v>
+        <v>5.332456557673562</v>
       </c>
       <c r="D19" t="n">
-        <v>29.76035705845253</v>
+        <v>4.836058021998537</v>
       </c>
       <c r="E19" t="n">
-        <v>15.52891954370692</v>
+        <v>2.523449425852375</v>
       </c>
       <c r="F19" t="n">
-        <v>21.57872834077787</v>
+        <v>3.506543355376404</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
